--- a/Bike-Repair-Source-Workbooks/Income-Statement-Steps.xlsx
+++ b/Bike-Repair-Source-Workbooks/Income-Statement-Steps.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ra1/Courses-Local/Instructional_Redesign_v2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ra1/Courses-Local/Instructional_Redesign_v2/Bike-Repair-Source-Workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_BFB844E890CE1126E7FEE944A15CF5079546EBBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_69245AB878EE5DE0CAB807E4BA255D1C80B0C3A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="3000" windowWidth="33460" windowHeight="26100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="3000" windowWidth="33460" windowHeight="26100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0 · Data copied in" sheetId="1" r:id="rId1"/>
@@ -1700,7 +1700,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:D56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -1725,7 +1725,7 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>27</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>31</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
         <v>35</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
         <v>37</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>44</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
         <v>46</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
         <v>48</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
         <v>50</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
         <v>52</v>
       </c>
@@ -1910,7 +1910,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
         <v>11</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B30" s="3" t="s">
         <v>13</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B31" s="3" t="s">
         <v>16</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
         <v>18</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B33" s="3" t="s">
         <v>21</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B34" s="3" t="s">
         <v>23</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B35" s="3" t="s">
         <v>25</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>-65</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="3" t="s">
         <v>26</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="3" t="s">
         <v>28</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="3" t="s">
         <v>30</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B39" s="3" t="s">
         <v>32</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>-125</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B40" s="3" t="s">
         <v>34</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>-55</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B42" s="3" t="s">
         <v>38</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B43" s="3" t="s">
         <v>40</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B44" s="3" t="s">
         <v>41</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B45" s="3" t="s">
         <v>43</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B46" s="3" t="s">
         <v>45</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>-129</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B47" s="3" t="s">
         <v>47</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>-70</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B48" s="3" t="s">
         <v>49</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B49" s="3" t="s">
         <v>51</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B50" s="3" t="s">
         <v>53</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>-36</v>
       </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B51" s="3" t="s">
         <v>54</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B52" s="3" t="s">
         <v>55</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B53" s="3" t="s">
         <v>56</v>
       </c>
@@ -2457,7 +2457,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:D43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -2496,7 +2496,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>63</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>64</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
         <v>65</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>66</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
         <v>67</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>68</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>-65</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>69</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>70</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
         <v>71</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>-125</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
         <v>72</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>-55</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
         <v>73</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
         <v>74</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
         <v>75</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>76</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
         <v>77</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>-129</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
         <v>78</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>-70</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
         <v>79</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
         <v>80</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
         <v>81</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B30" s="3" t="s">
         <v>83</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B31" s="3" t="s">
         <v>84</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B32" s="3" t="s">
         <v>85</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B36" s="3" t="s">
         <v>87</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="3" t="s">
         <v>88</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="3" t="s">
         <v>89</v>
       </c>

--- a/Bike-Repair-Source-Workbooks/Income-Statement-Steps.xlsx
+++ b/Bike-Repair-Source-Workbooks/Income-Statement-Steps.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D49"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -550,6 +550,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -1021,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D49"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1762,7 +1763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D56"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1785,6 +1786,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -2014,9 +2016,9 @@
       <c r="D26" s="11">
         <f>SUM(D5:D25)</f>
         <v>6020</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="8" t="inlineStr">
         <is>
@@ -2286,9 +2288,9 @@
       <c r="D54" s="11">
         <f>SUM(D29:D53)</f>
         <v>-3380</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="B56" s="9" t="inlineStr">
         <is>
@@ -2299,7 +2301,6 @@
       <c r="D56" s="11">
         <f>D26+D54</f>
         <v>2640</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -2313,7 +2314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D31"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2336,6 +2337,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="9" t="inlineStr">
         <is>
@@ -2347,6 +2349,7 @@
         <v>6020</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -2746,7 +2749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D43"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2769,6 +2772,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="9" t="inlineStr">
         <is>
@@ -2780,6 +2784,7 @@
         <v>6020</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -2995,9 +3000,9 @@
       <c r="D27" s="14">
         <f>SUM(D8:D26)</f>
         <v>-1200</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="13" t="inlineStr">
         <is>
@@ -3044,9 +3049,9 @@
       <c r="D33" s="14">
         <f>SUM(D30:D32)</f>
         <v>-1950</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="B35" s="13" t="inlineStr">
         <is>
@@ -3093,9 +3098,9 @@
       <c r="D39" s="14">
         <f>SUM(D36:D38)</f>
         <v>-230</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="B41" s="9" t="inlineStr">
         <is>
@@ -3106,9 +3111,9 @@
       <c r="D41" s="11">
         <f>D27+D33+D39</f>
         <v>-3380</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="B43" s="9" t="inlineStr">
         <is>
@@ -3119,7 +3124,6 @@
       <c r="D43" s="11">
         <f>6020+D41</f>
         <v>2640</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -3133,7 +3137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3156,6 +3160,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -3185,9 +3190,9 @@
       <c r="D6" s="16">
         <f>D5</f>
         <v>6020</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -3237,9 +3242,9 @@
       <c r="D12" s="16">
         <f>SUM(D9:D11)</f>
         <v>3380</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -3250,7 +3255,6 @@
       <c r="D14" s="16">
         <f>D6-D12</f>
         <v>2640</v>
-        <v/>
       </c>
     </row>
   </sheetData>
